--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4019,20 +4019,14 @@
           <t>p0lFJwSk</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B225" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="226">
@@ -4041,20 +4035,14 @@
           <t>vNmJIcsd</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B226" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D226" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="227">
@@ -4063,20 +4051,14 @@
           <t>MHXbihN8</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="228">
@@ -4085,20 +4067,14 @@
           <t>69kBKJCq</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B228" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="229">
@@ -4107,20 +4083,14 @@
           <t>h29zRLZF</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B229" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -4129,20 +4099,14 @@
           <t>QF7rPa4S</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B230" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D230" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="231">
@@ -4151,20 +4115,14 @@
           <t>nP8vQukM</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B231" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="232">
@@ -4173,20 +4131,14 @@
           <t>AszX60rp</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B232" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D232" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="233">
@@ -4195,20 +4147,14 @@
           <t>jix3jCxF</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B233" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D233" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="234">
@@ -4217,20 +4163,14 @@
           <t>h6Py6Kcj</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B234" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="235">
@@ -4239,20 +4179,14 @@
           <t>WdOu5vDd</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B235" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="236">
@@ -4261,20 +4195,14 @@
           <t>KCHNTNkc</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B236" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D236" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="237">
@@ -4283,20 +4211,14 @@
           <t>b3GRSs53</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B237" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="238">
@@ -4305,19 +4227,673 @@
           <t>tS5WR1K9</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>5.25</t>
+      <c r="B238" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D238" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>632gURJ8</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>IcKcrkcE</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>CKJ1s9CK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>E5m1wufk</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>MVj9yJO1</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>0MkDzwv8</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>rHDMpN1F</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>S8i5xa9e</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>v7LgqVs8</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>WtbdvLvq</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>nkKDnqX2</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>UXBUr1WR</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>M7CQqsHL</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>0hOHo3n9</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>YoWVNaf2</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>feXROuud</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>hEuyZP23</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>0vqqX3XF</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>MmpuYqI9</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>CI2lBMAd</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>bTwJQ1Aq</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>xKxNPLPk</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>ENtXZ5mc</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>r3YmWNnM</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>tliiVs2S</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SSyDUABH</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>4hatDrtp</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>bFbpC2ej</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>nHKFVjdB</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>00I3YhCh</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2.62</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4243,20 +4243,14 @@
           <t>632gURJ8</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
+      <c r="B239" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="240">
@@ -4265,20 +4259,14 @@
           <t>IcKcrkcE</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B240" t="n">
+        <v>3</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D240" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="241">
@@ -4287,20 +4275,14 @@
           <t>CKJ1s9CK</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B241" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="242">
@@ -4309,20 +4291,14 @@
           <t>E5m1wufk</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="B242" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="243">
@@ -4331,20 +4307,14 @@
           <t>MVj9yJO1</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B243" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="244">
@@ -4353,20 +4323,14 @@
           <t>0MkDzwv8</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B244" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="245">
@@ -4375,20 +4339,14 @@
           <t>rHDMpN1F</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B245" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="246">
@@ -4397,20 +4355,14 @@
           <t>S8i5xa9e</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="247">
@@ -4419,20 +4371,14 @@
           <t>v7LgqVs8</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B247" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D247" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="248">
@@ -4441,20 +4387,14 @@
           <t>WtbdvLvq</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="249">
@@ -4463,20 +4403,14 @@
           <t>nkKDnqX2</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>4.62</t>
-        </is>
+      <c r="B249" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D249" t="n">
+        <v>4.62</v>
       </c>
     </row>
     <row r="250">
@@ -4485,20 +4419,14 @@
           <t>UXBUr1WR</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B250" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D250" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -4507,20 +4435,14 @@
           <t>M7CQqsHL</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B251" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="252">
@@ -4529,20 +4451,14 @@
           <t>0hOHo3n9</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>7.40</t>
-        </is>
+      <c r="B252" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C252" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D252" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="253">
@@ -4551,20 +4467,14 @@
           <t>YoWVNaf2</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
+      <c r="B253" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D253" t="n">
+        <v>4.35</v>
       </c>
     </row>
     <row r="254">
@@ -4573,20 +4483,14 @@
           <t>feXROuud</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B254" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="255">
@@ -4595,20 +4499,14 @@
           <t>hEuyZP23</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B255" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="256">
@@ -4617,20 +4515,14 @@
           <t>0vqqX3XF</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B256" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="257">
@@ -4639,20 +4531,14 @@
           <t>MmpuYqI9</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B257" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C257" t="n">
+        <v>5</v>
+      </c>
+      <c r="D257" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -4661,20 +4547,14 @@
           <t>CI2lBMAd</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
+      <c r="B258" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D258" t="n">
+        <v>4.55</v>
       </c>
     </row>
     <row r="259">
@@ -4683,20 +4563,14 @@
           <t>bTwJQ1Aq</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B259" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="260">
@@ -4705,20 +4579,14 @@
           <t>xKxNPLPk</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B260" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="261">
@@ -4727,20 +4595,14 @@
           <t>ENtXZ5mc</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B261" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D261" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="262">
@@ -4749,20 +4611,14 @@
           <t>r3YmWNnM</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B262" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="263">
@@ -4771,20 +4627,14 @@
           <t>tliiVs2S</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B263" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D263" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="264">
@@ -4793,20 +4643,14 @@
           <t>SSyDUABH</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B264" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="265">
@@ -4815,20 +4659,14 @@
           <t>4hatDrtp</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B265" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="266">
@@ -4837,20 +4675,14 @@
           <t>bFbpC2ej</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B266" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="267">
@@ -4859,20 +4691,14 @@
           <t>nHKFVjdB</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B267" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D267" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="268">
@@ -4881,19 +4707,1729 @@
           <t>00I3YhCh</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D268" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>rkXKkQTD</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>AqTyT2M0</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>46SuSMy7</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>rcRqRtiD</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>dtPXTr7f</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2iXrs8a1</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>zRzPV4xr</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>EHZSUOil</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>Aqipwmp8</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>MJflx7aE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>rkHsqUUl</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>4rpgyREK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>rZrczoUQ</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>MuGorlpe</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>juKJMRaR</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Ik4bFqh1</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>dt32E377</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>0E9gGPxe</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>lSHwpAFr</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>MNAkH5Nl</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>S0BoIo8r</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>C6QBlj7R</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>dbI3Q902</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>8GUEN7pL</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>hQiNHHd2</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>UXmi590d</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>8MoOBBNS</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>jskm6koj</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>IXhBEDwA</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>0drGDXhG</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>AVXk7VVq</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>A7k3GZ8c</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>vsf7FgO3</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>xzDc13GK</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>EanKCi8M</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>WGjaHFgi</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Eo7obhgT</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>WQgDgC1p</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>p6FU1zf4</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>IJDx0EOG</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>ze8saYwN</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>AmNH4xAo</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>tYn8pZOT</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
         <is>
           <t>2.62</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2.62</t>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>rsZZugXp</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>8.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>vTEY0f9A</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>UBCGhWGj</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>lvML3dPi</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>W2BQ2Gvb</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>b9c3oF9N</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>GQ1rjweh</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>M32viJun</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>jqfemyuB</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ATbzhaQu</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>AkdSq2YI</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>CheilHP4</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>p6ganefH</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>WbcOprJC</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>fH0nkcAb</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2PhKoO36</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>OYgGn4l0</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>tA4BmpZg</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>YDtwhVka</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>S607lQJm</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>4ErueStK</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>x23tzR4f</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>bHikY4Z6</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>QNqyd8RD</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>8Sbxy7kl</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>Gh2pZpK0</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>Uy0Yymzr</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>CKegXOlD</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>Yq13k64s</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>WzFyfndQ</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>OfN5tTRQ</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>4.00</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5971,20 +5971,14 @@
           <t>trWntSE7</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B347" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C347" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D347" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="348">
@@ -5993,20 +5987,14 @@
           <t>SvbdWyTh</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B348" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D348" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="349">
@@ -6015,20 +6003,14 @@
           <t>AoWGqXpJ</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B349" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C349" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D349" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="350">
@@ -6037,20 +6019,14 @@
           <t>hIoLKAg0</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B350" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C350" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D350" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="351">
@@ -6059,20 +6035,14 @@
           <t>KEflYcbt</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B351" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C351" t="n">
+        <v>4</v>
+      </c>
+      <c r="D351" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="352">
@@ -6081,20 +6051,14 @@
           <t>EyfhXHDn</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B352" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C352" t="n">
+        <v>4</v>
+      </c>
+      <c r="D352" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="353">
@@ -6103,20 +6067,14 @@
           <t>ryEQJ8Fk</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B353" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C353" t="n">
+        <v>3</v>
+      </c>
+      <c r="D353" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="354">
@@ -6125,20 +6083,14 @@
           <t>nTYkQAxM</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B354" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C354" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="355">
@@ -6147,20 +6099,14 @@
           <t>QJXgPUiS</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B355" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C355" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D355" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="356">
@@ -6169,20 +6115,14 @@
           <t>IgUoRjNF</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="B356" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C356" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D356" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="357">
@@ -6191,20 +6131,14 @@
           <t>xbDUISUe</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B357" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C357" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D357" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="358">
@@ -6213,20 +6147,14 @@
           <t>W0AMKl0q</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B358" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C358" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D358" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="359">
@@ -6235,20 +6163,14 @@
           <t>GlCYHnp2</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B359" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C359" t="n">
+        <v>3</v>
+      </c>
+      <c r="D359" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="360">
@@ -6257,20 +6179,14 @@
           <t>v3VsSW79</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B360" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C360" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D360" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="361">
@@ -6279,20 +6195,14 @@
           <t>dvtwTCh3</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B361" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C361" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D361" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="362">
@@ -6301,19 +6211,79 @@
           <t>ryxZThwc</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>6.15</t>
+      <c r="B362" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C362" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D362" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>WdfLujx9</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>h6eHtWM2</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>QJgPvAiF</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>5.50</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D405"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6691,20 +6691,14 @@
           <t>xhnHdYtb</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B392" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C392" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D392" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="393">
@@ -6713,20 +6707,14 @@
           <t>GroLehd4</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B393" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C393" t="n">
+        <v>4</v>
+      </c>
+      <c r="D393" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="394">
@@ -6735,20 +6723,14 @@
           <t>YJuQfCBA</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B394" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C394" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D394" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="395">
@@ -6757,20 +6739,14 @@
           <t>rVnDcERi</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B395" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C395" t="n">
+        <v>4</v>
+      </c>
+      <c r="D395" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="396">
@@ -6779,20 +6755,14 @@
           <t>0n3Ddmal</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B396" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C396" t="n">
+        <v>4</v>
+      </c>
+      <c r="D396" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="397">
@@ -6801,20 +6771,14 @@
           <t>SM4QZAZp</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B397" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C397" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D397" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="398">
@@ -6823,20 +6787,14 @@
           <t>URr9bfCo</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B398" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C398" t="n">
+        <v>4</v>
+      </c>
+      <c r="D398" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="399">
@@ -6845,20 +6803,14 @@
           <t>QDIbviRT</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B399" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C399" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D399" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="400">
@@ -6867,20 +6819,14 @@
           <t>ImJfuXBN</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B400" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C400" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D400" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="401">
@@ -6889,20 +6835,14 @@
           <t>dYUosgsB</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B401" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C401" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D401" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="402">
@@ -6911,20 +6851,14 @@
           <t>U3Cs29yR</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B402" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C402" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D402" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="403">
@@ -6933,20 +6867,14 @@
           <t>vcKjtDdH</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B403" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C403" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D403" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="404">
@@ -6955,20 +6883,14 @@
           <t>Me49cTqr</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D404" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="405">
@@ -6977,19 +6899,563 @@
           <t>SYdMjeTC</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
+      <c r="B405" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C405" t="n">
+        <v>3</v>
+      </c>
+      <c r="D405" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>bR2B69AM</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>zJAPgoq7</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>Kz477keG</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>tdBLfRT0</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>QD438VuA</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2uJ8nlJj</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>jeCjBXei</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>CA0a9BQ3</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>UoBfAiBc</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>rBhIe7Ef</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>I7sxhAeT</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>OlK4mU3p</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>6XwYhjtN</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>CAvUgWQG</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>p2PIpxK5</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>vPOMqdZB</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>6exiWx5C</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>GQJsg0CP</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>Qa9Hnbkg</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>hnB9lKKt</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>zVteVdKI</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>S4wmXIk6</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>n9ADmvzm</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>6BQEoI4a</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>ELuaUGZO</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>3.00</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6915,20 +6915,14 @@
           <t>bR2B69AM</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B406" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C406" t="n">
+        <v>4</v>
+      </c>
+      <c r="D406" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="407">
@@ -6937,20 +6931,14 @@
           <t>zJAPgoq7</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B407" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C407" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D407" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="408">
@@ -6959,20 +6947,14 @@
           <t>Kz477keG</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B408" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C408" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D408" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="409">
@@ -6981,20 +6963,14 @@
           <t>tdBLfRT0</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B409" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C409" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D409" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="410">
@@ -7003,20 +6979,14 @@
           <t>QD438VuA</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B410" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C410" t="n">
+        <v>4</v>
+      </c>
+      <c r="D410" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="411">
@@ -7025,20 +6995,14 @@
           <t>2uJ8nlJj</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B411" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C411" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D411" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="412">
@@ -7047,20 +7011,14 @@
           <t>jeCjBXei</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B412" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C412" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D412" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="413">
@@ -7069,20 +7027,14 @@
           <t>CA0a9BQ3</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B413" t="n">
+        <v>3</v>
+      </c>
+      <c r="C413" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D413" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="414">
@@ -7091,20 +7043,14 @@
           <t>UoBfAiBc</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B414" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C414" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D414" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -7113,20 +7059,14 @@
           <t>rBhIe7Ef</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B415" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C415" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D415" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="416">
@@ -7135,20 +7075,14 @@
           <t>I7sxhAeT</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B416" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C416" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D416" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="417">
@@ -7157,20 +7091,14 @@
           <t>OlK4mU3p</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B417" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C417" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D417" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="418">
@@ -7179,20 +7107,14 @@
           <t>6XwYhjtN</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B418" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C418" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D418" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="419">
@@ -7201,20 +7123,14 @@
           <t>CAvUgWQG</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B419" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C419" t="n">
+        <v>4</v>
+      </c>
+      <c r="D419" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="420">
@@ -7223,20 +7139,14 @@
           <t>p2PIpxK5</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
+      <c r="B420" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C420" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D420" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="421">
@@ -7245,20 +7155,14 @@
           <t>vPOMqdZB</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B421" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C421" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D421" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="422">
@@ -7267,20 +7171,14 @@
           <t>6exiWx5C</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="B422" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C422" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D422" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="423">
@@ -7289,20 +7187,14 @@
           <t>GQJsg0CP</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B423" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C423" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D423" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="424">
@@ -7311,20 +7203,14 @@
           <t>Qa9Hnbkg</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
+      <c r="B424" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C424" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D424" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="425">
@@ -7333,20 +7219,14 @@
           <t>hnB9lKKt</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B425" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C425" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D425" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="426">
@@ -7355,20 +7235,14 @@
           <t>zVteVdKI</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
+      <c r="B426" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="C426" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D426" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="427">
@@ -7377,20 +7251,14 @@
           <t>S4wmXIk6</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B427" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C427" t="n">
+        <v>4</v>
+      </c>
+      <c r="D427" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="428">
@@ -7399,20 +7267,14 @@
           <t>n9ADmvzm</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="B428" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C428" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D428" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="429">
@@ -7421,20 +7283,14 @@
           <t>6BQEoI4a</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
+      <c r="B429" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C429" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D429" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="430">
@@ -7443,19 +7299,585 @@
           <t>ELuaUGZO</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
+      <c r="B430" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C430" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D430" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>AwME1KOf</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>3.00</t>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>E99Th5bD</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>ph6YLlA9</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>UHiGG8jK</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>Or5xL8PF</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>4tJ63tfr</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>GGMA209l</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>jRhCHlyE</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>SdLZ0mYq</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>QmZ75TPS</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>MJKw07mj</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>zNOsaR2d</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>xS2QNAuc</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>GI1UMUf3</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>ID0yCpq9</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>Eed8egYN</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>z5c4dZIH</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>46dq1c4n</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>QFcu2wkt</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>pG4iayZb</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>ziIVsz4O</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>ptlrYbz0</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>EsHZtfJU</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>nVol0HJh</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>IT2acF3B</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>hSSQrGlI</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
